--- a/data/trans_bre/P6904-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 34,37</t>
+          <t>-6,78; 34,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 25,44</t>
+          <t>-15,86; 22,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 39,91</t>
+          <t>-0,61; 41,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 1,67</t>
+          <t>-30,6; -0,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 81,43</t>
+          <t>-13,0; 78,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 52,9</t>
+          <t>-25,39; 46,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 101,1</t>
+          <t>-0,79; 101,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 1,21</t>
+          <t>-37,5; -0,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 11,08</t>
+          <t>-20,86; 11,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 13,68</t>
+          <t>-23,14; 12,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 16,64</t>
+          <t>-16,83; 16,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 13,08</t>
+          <t>-14,66; 10,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 24,85</t>
+          <t>-40,8; 26,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 27,26</t>
+          <t>-34,11; 25,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 27,27</t>
+          <t>-22,97; 27,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 23,94</t>
+          <t>-20,24; 17,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 25,17</t>
+          <t>-9,85; 24,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,51; -0,05</t>
+          <t>-33,64; 0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 25,47</t>
+          <t>-2,19; 26,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 58,39</t>
+          <t>8,8; 60,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 52,24</t>
+          <t>-16,7; 49,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 0,06</t>
+          <t>-55,02; 1,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 48,74</t>
+          <t>-2,75; 52,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,19; 242,95</t>
+          <t>18,79; 258,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 7,14</t>
+          <t>-21,45; 5,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 23,71</t>
+          <t>-9,32; 25,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 18,29</t>
+          <t>-13,72; 17,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 19,51</t>
+          <t>-6,82; 18,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 14,55</t>
+          <t>-36,0; 12,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 62,03</t>
+          <t>-19,01; 71,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 34,88</t>
+          <t>-21,63; 34,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 37,96</t>
+          <t>-9,91; 35,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,74</t>
+          <t>-8,75; 8,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 5,03</t>
+          <t>-11,66; 5,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 16,18</t>
+          <t>-0,49; 16,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 15,77</t>
+          <t>-4,16; 16,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 15,39</t>
+          <t>-15,95; 17,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 9,79</t>
+          <t>-20,07; 10,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 29,22</t>
+          <t>-0,73; 29,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 27,33</t>
+          <t>-6,62; 29,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6904-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-15,0</t>
+          <t>-16,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,74%</t>
+          <t>-21,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 34,0</t>
+          <t>-5,98; 32,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 22,77</t>
+          <t>-18,86; 23,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 41,92</t>
+          <t>-3,15; 39,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,6; -0,37</t>
+          <t>-31,26; -1,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 78,66</t>
+          <t>-10,8; 75,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 46,76</t>
+          <t>-29,74; 46,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 101,42</t>
+          <t>-2,62; 100,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,5; -0,6</t>
+          <t>-37,12; -1,76</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,06%</t>
+          <t>-5,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 11,77</t>
+          <t>-20,37; 12,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 12,84</t>
+          <t>-19,8; 14,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 16,19</t>
+          <t>-16,16; 16,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 10,27</t>
+          <t>-16,2; 8,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 26,69</t>
+          <t>-41,15; 29,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 25,46</t>
+          <t>-30,69; 29,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 27,57</t>
+          <t>-22,37; 27,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 17,9</t>
+          <t>-22,56; 14,86</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,14</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 24,15</t>
+          <t>-10,6; 24,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 0,64</t>
+          <t>-36,58; 0,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 26,67</t>
+          <t>-4,02; 25,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 60,23</t>
+          <t>-13,3; 22,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 49,82</t>
+          <t>-16,65; 48,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 1,39</t>
+          <t>-57,17; 2,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 52,76</t>
+          <t>-5,87; 52,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 258,26</t>
+          <t>-23,91; 60,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 5,87</t>
+          <t>-22,12; 5,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 25,72</t>
+          <t>-8,58; 25,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 17,49</t>
+          <t>-14,95; 18,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 18,68</t>
+          <t>-8,96; 17,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 12,56</t>
+          <t>-36,51; 12,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 71,33</t>
+          <t>-16,47; 70,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 34,92</t>
+          <t>-23,95; 34,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 35,1</t>
+          <t>-13,2; 31,5</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>-3,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 8,36</t>
+          <t>-8,72; 7,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 5,43</t>
+          <t>-12,06; 5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 16,47</t>
+          <t>-1,05; 15,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,37</t>
+          <t>-9,12; 4,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 17,22</t>
+          <t>-15,42; 15,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 10,93</t>
+          <t>-20,8; 11,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 29,48</t>
+          <t>-1,7; 28,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 29,39</t>
+          <t>-13,64; 7,32</t>
         </is>
       </c>
     </row>
